--- a/data/multiplicadores/multiplicadores_renda.xlsx
+++ b/data/multiplicadores/multiplicadores_renda.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7cfd6d076248aa8/Documents/Study/UFV/Mestrado/4º Semestre/ERU 799 - Pesquisa/Estimação/mip-energia/data/multiplicadores/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b7cfd6d076248aa8/Documents/Study/UFV/Mestrado/4º Semestre (2025-2)/ERU 799 - Pesquisa/Estimação/mip-energia/data/multiplicadores/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_4575F98F1D41680F62355476585DCE3A874731B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0F1FA83-2F76-448A-8B78-75CB1E3CC25F}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_4575F98F1D41680F62355476585DCE3A874731B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86268471-1A61-48D6-8DFC-B6F0FB2CA453}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -654,1468 +654,1468 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>288936.3935269349</v>
+        <v>217110.58456947279</v>
       </c>
       <c r="D2">
-        <v>552073.00000004855</v>
+        <v>398037.00000000099</v>
       </c>
       <c r="E2">
-        <v>0.7259033545296899</v>
+        <v>0.54545327336270799</v>
       </c>
       <c r="F2">
-        <v>4.148150777409243</v>
+        <v>2.077776775364391</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C3">
-        <v>-74775.998329780705</v>
+        <v>296215.43115909322</v>
       </c>
       <c r="D3">
-        <v>1120579</v>
+        <v>151959.00000000061</v>
       </c>
       <c r="E3">
-        <v>-0.18786192823727571</v>
+        <v>0.74419069372719726</v>
       </c>
       <c r="F3">
-        <v>3.5695134147015342</v>
+        <v>1.4296748233183869</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="C4">
-        <v>250627.71528127551</v>
+        <v>382066.6850712974</v>
       </c>
       <c r="D4">
-        <v>231741.35660714979</v>
+        <v>37870.000000000036</v>
       </c>
       <c r="E4">
-        <v>0.62965934142121172</v>
+        <v>0.95987731057991199</v>
       </c>
       <c r="F4">
-        <v>3.206609381841123</v>
+        <v>1.073089160258085</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>342276.64617695921</v>
+        <v>379528.21906052699</v>
       </c>
       <c r="D5">
-        <v>292406.00000000309</v>
+        <v>20011.000000000651</v>
       </c>
       <c r="E5">
-        <v>0.85991163177533325</v>
+        <v>0.95349984815614153</v>
       </c>
       <c r="F5">
-        <v>2.842805847987774</v>
+        <v>1.065984153340336</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="C6">
-        <v>370926.45426484832</v>
+        <v>264629.86238564592</v>
       </c>
       <c r="D6">
-        <v>858764</v>
+        <v>225938</v>
       </c>
       <c r="E6">
-        <v>0.93188938280824996</v>
+        <v>0.66483734523585802</v>
       </c>
       <c r="F6">
-        <v>2.701600652449093</v>
+        <v>1.8644108023105219</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>97768.138192318089</v>
+        <v>379024.87283754692</v>
       </c>
       <c r="D7">
-        <v>433811.26648911083</v>
+        <v>92326.00000000032</v>
       </c>
       <c r="E7">
-        <v>0.24562575386790131</v>
+        <v>0.95223527671434038</v>
       </c>
       <c r="F7">
-        <v>2.651047467128635</v>
+        <v>1.3568178072692281</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>305971.02780898742</v>
+        <v>389688.98990794591</v>
       </c>
       <c r="D8">
-        <v>150065.03251769711</v>
+        <v>18272.999999999829</v>
       </c>
       <c r="E8">
-        <v>0.7686999645987348</v>
+        <v>0.97902705001782464</v>
       </c>
       <c r="F8">
-        <v>2.6069007781586939</v>
+        <v>1.115205158173777</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>388717.00456222729</v>
+        <v>342276.64617695921</v>
       </c>
       <c r="D9">
-        <v>187915.00000000509</v>
+        <v>292406.00000000309</v>
       </c>
       <c r="E9">
-        <v>0.97658510279754496</v>
+        <v>0.85991163177533325</v>
       </c>
       <c r="F9">
-        <v>2.5941798690936539</v>
+        <v>2.842805847987774</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>294385.87240643782</v>
+        <v>379770.9722566437</v>
       </c>
       <c r="D10">
-        <v>324942.99999999697</v>
+        <v>51555.000000003318</v>
       </c>
       <c r="E10">
-        <v>0.73959423974765415</v>
+        <v>0.95410972411268991</v>
       </c>
       <c r="F10">
-        <v>2.5093867624001982</v>
+        <v>1.2220129114287359</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>133659.0285927371</v>
+        <v>294385.87240643782</v>
       </c>
       <c r="D11">
-        <v>398813.04492834641</v>
+        <v>324942.99999999697</v>
       </c>
       <c r="E11">
-        <v>0.3357954878384089</v>
+        <v>0.73959423974765415</v>
       </c>
       <c r="F11">
-        <v>2.4463314185194158</v>
+        <v>2.5093867624001982</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>58</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>357555.66717477358</v>
+        <v>363214.13428197149</v>
       </c>
       <c r="D12">
-        <v>276938.00000003021</v>
+        <v>78544.000000008746</v>
       </c>
       <c r="E12">
-        <v>0.89829756322847543</v>
+        <v>0.91251349568500062</v>
       </c>
       <c r="F12">
-        <v>2.1284300920489199</v>
+        <v>1.478254227533303</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>217110.58456947279</v>
+        <v>397659.15418979042</v>
       </c>
       <c r="D13">
-        <v>398037.00000000099</v>
+        <v>15694.00000000024</v>
       </c>
       <c r="E13">
-        <v>0.54545327336270799</v>
+        <v>0.99905072691681784</v>
       </c>
       <c r="F13">
-        <v>2.077776775364391</v>
+        <v>1.08419059113002</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>298315.80931657011</v>
+        <v>365806.76696825738</v>
       </c>
       <c r="D14">
-        <v>104820.0000000031</v>
+        <v>54793.000000011139</v>
       </c>
       <c r="E14">
-        <v>0.74946753522051801</v>
+        <v>0.91902704263235946</v>
       </c>
       <c r="F14">
-        <v>2.0741650792052369</v>
+        <v>1.284379902515564</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>264629.86238564592</v>
+        <v>392018.60950809799</v>
       </c>
       <c r="D15">
-        <v>225938</v>
+        <v>66432.000000002095</v>
       </c>
       <c r="E15">
-        <v>0.66483734523585802</v>
+        <v>0.98487982149422548</v>
       </c>
       <c r="F15">
-        <v>1.8644108023105219</v>
+        <v>1.438533432850309</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>362015.74285358918</v>
+        <v>393217.75290255662</v>
       </c>
       <c r="D16">
-        <v>302873.0000000092</v>
+        <v>43848.000000000589</v>
       </c>
       <c r="E16">
-        <v>0.90950274183954838</v>
+        <v>0.98789246452605051</v>
       </c>
       <c r="F16">
-        <v>1.821848478591946</v>
+        <v>1.2977517040723621</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>369491.98584294133</v>
+        <v>376540.32580867672</v>
       </c>
       <c r="D17">
-        <v>171919.00000001461</v>
+        <v>32687.000000022239</v>
       </c>
       <c r="E17">
-        <v>0.92828552582533885</v>
+        <v>0.94599327652624188</v>
       </c>
       <c r="F17">
-        <v>1.8147017381297319</v>
+        <v>1.2701372486258291</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>353030.49101966218</v>
+        <v>337750.34982208698</v>
       </c>
       <c r="D18">
-        <v>73148.000000061249</v>
+        <v>109595.0000000502</v>
       </c>
       <c r="E18">
-        <v>0.88692883078623685</v>
+        <v>0.84854008502246314</v>
       </c>
       <c r="F18">
-        <v>1.7761362198031481</v>
+        <v>1.6758267253045189</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>357386.79530774523</v>
+        <v>377734.50221215922</v>
       </c>
       <c r="D19">
-        <v>129313.0000000104</v>
+        <v>21333.000000031148</v>
       </c>
       <c r="E19">
-        <v>0.89787330149645472</v>
+        <v>0.94899344084132431</v>
       </c>
       <c r="F19">
-        <v>1.7385924810195641</v>
+        <v>1.08956589969713</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>337750.34982208698</v>
+        <v>97768.138192318089</v>
       </c>
       <c r="D20">
-        <v>109595.0000000502</v>
+        <v>433811.26648911083</v>
       </c>
       <c r="E20">
-        <v>0.84854008502246314</v>
+        <v>0.24562575386790131</v>
       </c>
       <c r="F20">
-        <v>1.6758267253045189</v>
+        <v>2.651047467128635</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>395028.47379474458</v>
+        <v>388101.79833486368</v>
       </c>
       <c r="D21">
-        <v>3303.8713821240121</v>
+        <v>10385.862128765169</v>
       </c>
       <c r="E21">
-        <v>0.99244159159762435</v>
+        <v>0.97503950219417468</v>
       </c>
       <c r="F21">
-        <v>1.670942610793051</v>
+        <v>1.0321144123808801</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>61</v>
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>332842.75692133512</v>
+        <v>395028.47379474458</v>
       </c>
       <c r="D22">
-        <v>166879.000000003</v>
+        <v>3303.8713821240121</v>
       </c>
       <c r="E22">
-        <v>0.83621059580223522</v>
+        <v>0.99244159159762435</v>
       </c>
       <c r="F22">
-        <v>1.6293767783199</v>
+        <v>1.670942610793051</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>242390.7076449458</v>
+        <v>373493.82720991608</v>
       </c>
       <c r="D23">
-        <v>179506</v>
+        <v>54637.000000001673</v>
       </c>
       <c r="E23">
-        <v>0.60896526615602364</v>
+        <v>0.93833946896875209</v>
       </c>
       <c r="F23">
-        <v>1.623818786226795</v>
+        <v>1.290996450391442</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C24">
-        <v>311255.42702130752</v>
+        <v>242390.7076449458</v>
       </c>
       <c r="D24">
-        <v>105992.00000002451</v>
+        <v>179506</v>
       </c>
       <c r="E24">
-        <v>0.78197611533929445</v>
+        <v>0.60896526615602364</v>
       </c>
       <c r="F24">
-        <v>1.6111050840490351</v>
+        <v>1.623818786226795</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>396542.59501553333</v>
+        <v>325015.43607161281</v>
       </c>
       <c r="D25">
-        <v>351095.00000001851</v>
+        <v>88307.86977582956</v>
       </c>
       <c r="E25">
-        <v>0.99624556263747421</v>
+        <v>0.81654578863676475</v>
       </c>
       <c r="F25">
-        <v>1.5807215816432709</v>
+        <v>1.325375273308447</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>321101.37912642211</v>
+        <v>387272.86206822318</v>
       </c>
       <c r="D26">
-        <v>101954.000000026</v>
+        <v>50175.904170072157</v>
       </c>
       <c r="E26">
-        <v>0.80671238886440533</v>
+        <v>0.97295694136028132</v>
       </c>
       <c r="F26">
-        <v>1.569996685252409</v>
+        <v>1.301335063744097</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="C27">
-        <v>343402.2709010446</v>
+        <v>376957.46621017618</v>
       </c>
       <c r="D27">
-        <v>175093.00000000029</v>
+        <v>76244.0000000078</v>
       </c>
       <c r="E27">
-        <v>0.86273957170073068</v>
+        <v>0.94704127056071485</v>
       </c>
       <c r="F27">
-        <v>1.5567694582122069</v>
+        <v>1.269801205820035</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C28">
-        <v>325321.90714911162</v>
+        <v>303447.84792611859</v>
       </c>
       <c r="D28">
-        <v>83887.9674075699</v>
+        <v>121217.0000000571</v>
       </c>
       <c r="E28">
-        <v>0.81731574489082859</v>
+        <v>0.76236090596129968</v>
       </c>
       <c r="F28">
-        <v>1.5557133567015979</v>
+        <v>1.463550422867266</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="C29">
-        <v>397618.86043577321</v>
+        <v>325321.90714911162</v>
       </c>
       <c r="D29">
-        <v>202716.0000000016</v>
+        <v>83887.9674075699</v>
       </c>
       <c r="E29">
-        <v>0.99894949573977354</v>
+        <v>0.81731574489082859</v>
       </c>
       <c r="F29">
-        <v>1.5425081148186379</v>
+        <v>1.5557133567015979</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C30">
-        <v>357919.56345407391</v>
+        <v>305971.02780898742</v>
       </c>
       <c r="D30">
-        <v>79945.000000031156</v>
+        <v>150065.03251769711</v>
       </c>
       <c r="E30">
-        <v>0.8992117904970468</v>
+        <v>0.7686999645987348</v>
       </c>
       <c r="F30">
-        <v>1.534971953132986</v>
+        <v>2.6069007781586939</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="C31">
-        <v>50764.519568364602</v>
+        <v>353030.49101966218</v>
       </c>
       <c r="D31">
-        <v>649009.00000027753</v>
+        <v>73148.000000061249</v>
       </c>
       <c r="E31">
-        <v>0.12753718766939881</v>
+        <v>0.88692883078623685</v>
       </c>
       <c r="F31">
-        <v>1.509741756225951</v>
+        <v>1.7761362198031481</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C32">
-        <v>378640.66456153349</v>
+        <v>321101.37912642211</v>
       </c>
       <c r="D32">
-        <v>75234.938746999134</v>
+        <v>101954.000000026</v>
       </c>
       <c r="E32">
-        <v>0.95127001902218267</v>
+        <v>0.80671238886440533</v>
       </c>
       <c r="F32">
-        <v>1.504077588087775</v>
+        <v>1.569996685252409</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C33">
-        <v>363214.13428197149</v>
+        <v>366658.90613435599</v>
       </c>
       <c r="D33">
-        <v>78544.000000008746</v>
+        <v>103544.000000003</v>
       </c>
       <c r="E33">
-        <v>0.91251349568500062</v>
+        <v>0.92116789678938171</v>
       </c>
       <c r="F33">
-        <v>1.478254227533303</v>
+        <v>1.42914560554138</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C34">
-        <v>303447.84792611859</v>
+        <v>357919.56345407391</v>
       </c>
       <c r="D34">
-        <v>121217.0000000571</v>
+        <v>79945.000000031156</v>
       </c>
       <c r="E34">
-        <v>0.76236090596129968</v>
+        <v>0.8992117904970468</v>
       </c>
       <c r="F34">
-        <v>1.463550422867266</v>
+        <v>1.534971953132986</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C35">
-        <v>392018.60950809799</v>
+        <v>357386.79530774523</v>
       </c>
       <c r="D35">
-        <v>66432.000000002095</v>
+        <v>129313.0000000104</v>
       </c>
       <c r="E35">
-        <v>0.98487982149422548</v>
+        <v>0.89787330149645472</v>
       </c>
       <c r="F35">
-        <v>1.438533432850309</v>
+        <v>1.7385924810195641</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C36">
-        <v>296215.43115909322</v>
+        <v>388717.00456222729</v>
       </c>
       <c r="D36">
-        <v>151959.00000000061</v>
+        <v>187915.00000000509</v>
       </c>
       <c r="E36">
-        <v>0.74419069372719726</v>
+        <v>0.97658510279754496</v>
       </c>
       <c r="F36">
-        <v>1.4296748233183869</v>
+        <v>2.5941798690936539</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C37">
-        <v>366658.90613435599</v>
+        <v>311255.42702130752</v>
       </c>
       <c r="D37">
-        <v>103544.000000003</v>
+        <v>105992.00000002451</v>
       </c>
       <c r="E37">
-        <v>0.92116789678938171</v>
+        <v>0.78197611533929445</v>
       </c>
       <c r="F37">
-        <v>1.42914560554138</v>
+        <v>1.6111050840490351</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C38">
-        <v>371206.34512957919</v>
+        <v>395876.7338892243</v>
       </c>
       <c r="D38">
-        <v>34484.752941129023</v>
+        <v>41813.000000002947</v>
       </c>
       <c r="E38">
-        <v>0.93259256081615105</v>
+        <v>0.99457270024953282</v>
       </c>
       <c r="F38">
-        <v>1.4105750214185091</v>
+        <v>1.1841501614195751</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C39">
-        <v>381984.63032664981</v>
+        <v>378640.66456153349</v>
       </c>
       <c r="D39">
-        <v>143437.0000000103</v>
+        <v>75234.938746999134</v>
       </c>
       <c r="E39">
-        <v>0.95967116204435488</v>
+        <v>0.95127001902218267</v>
       </c>
       <c r="F39">
-        <v>1.382105547295928</v>
+        <v>1.504077588087775</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C40">
-        <v>379024.87283754692</v>
+        <v>332764.78614839731</v>
       </c>
       <c r="D40">
-        <v>92326.00000000032</v>
+        <v>79968.000000001339</v>
       </c>
       <c r="E40">
-        <v>0.95223527671434038</v>
+        <v>0.83601470754828444</v>
       </c>
       <c r="F40">
-        <v>1.3568178072692281</v>
+        <v>1.2781626565336579</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="C41">
-        <v>325015.43607161281</v>
+        <v>250627.71528127551</v>
       </c>
       <c r="D41">
-        <v>88307.86977582956</v>
+        <v>231741.35660714979</v>
       </c>
       <c r="E41">
-        <v>0.81654578863676475</v>
+        <v>0.62965934142121172</v>
       </c>
       <c r="F41">
-        <v>1.325375273308447</v>
+        <v>3.206609381841123</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C42">
-        <v>387272.86206822318</v>
+        <v>371206.34512957919</v>
       </c>
       <c r="D42">
-        <v>50175.904170072157</v>
+        <v>34484.752941129023</v>
       </c>
       <c r="E42">
-        <v>0.97295694136028132</v>
+        <v>0.93259256081615105</v>
       </c>
       <c r="F42">
-        <v>1.301335063744097</v>
+        <v>1.4105750214185091</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C43">
-        <v>393217.75290255662</v>
+        <v>381336.42890785559</v>
       </c>
       <c r="D43">
-        <v>43848.000000000589</v>
+        <v>16753.73575226765</v>
       </c>
       <c r="E43">
-        <v>0.98789246452605051</v>
+        <v>0.95804266665625226</v>
       </c>
       <c r="F43">
-        <v>1.2977517040723621</v>
+        <v>1.0076493450575259</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C44">
-        <v>302885.98128337623</v>
+        <v>367996.0624382025</v>
       </c>
       <c r="D44">
-        <v>138844.00000002471</v>
+        <v>40159.15469945356</v>
       </c>
       <c r="E44">
-        <v>0.76094931195686699</v>
+        <v>0.92452727369114329</v>
       </c>
       <c r="F44">
-        <v>1.297355576081316</v>
+        <v>1.108548303911296</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C45">
-        <v>195295.68846067501</v>
+        <v>349959.25602722663</v>
       </c>
       <c r="D45">
-        <v>261715.00000003359</v>
+        <v>82219.993974276586</v>
       </c>
       <c r="E45">
-        <v>0.49064707165583732</v>
+        <v>0.87921287726323361</v>
       </c>
       <c r="F45">
-        <v>1.296521423525953</v>
+        <v>1.179137830043024</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="C46">
-        <v>373493.82720991608</v>
+        <v>288936.3935269349</v>
       </c>
       <c r="D46">
-        <v>54637.000000001673</v>
+        <v>552073.00000004855</v>
       </c>
       <c r="E46">
-        <v>0.93833946896875209</v>
+        <v>0.7259033545296899</v>
       </c>
       <c r="F46">
-        <v>1.290996450391442</v>
+        <v>4.148150777409243</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="C47">
-        <v>365806.76696825738</v>
+        <v>343402.2709010446</v>
       </c>
       <c r="D47">
-        <v>54793.000000011139</v>
+        <v>175093.00000000029</v>
       </c>
       <c r="E47">
-        <v>0.91902704263235946</v>
+        <v>0.86273957170073068</v>
       </c>
       <c r="F47">
-        <v>1.284379902515564</v>
+        <v>1.5567694582122069</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C48">
-        <v>332764.78614839731</v>
+        <v>-74775.998329780705</v>
       </c>
       <c r="D48">
-        <v>79968.000000001339</v>
+        <v>1120579</v>
       </c>
       <c r="E48">
-        <v>0.83601470754828444</v>
+        <v>-0.18786192823727571</v>
       </c>
       <c r="F48">
-        <v>1.2781626565336579</v>
+        <v>3.5695134147015342</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C49">
-        <v>376540.32580867672</v>
+        <v>133659.0285927371</v>
       </c>
       <c r="D49">
-        <v>32687.000000022239</v>
+        <v>398813.04492834641</v>
       </c>
       <c r="E49">
-        <v>0.94599327652624188</v>
+        <v>0.3357954878384089</v>
       </c>
       <c r="F49">
-        <v>1.2701372486258291</v>
+        <v>2.4463314185194158</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C50">
-        <v>376957.46621017618</v>
+        <v>382946.31447513209</v>
       </c>
       <c r="D50">
-        <v>76244.0000000078</v>
+        <v>23042.0000000125</v>
       </c>
       <c r="E50">
-        <v>0.94704127056071485</v>
+        <v>0.9620872292654481</v>
       </c>
       <c r="F50">
-        <v>1.269801205820035</v>
+        <v>1.0997739167522951</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
         <v>55</v>
       </c>
-      <c r="B51" t="s">
-        <v>60</v>
-      </c>
       <c r="C51">
-        <v>356694.29340278561</v>
+        <v>371398.44608248671</v>
       </c>
       <c r="D51">
-        <v>43874.00000000115</v>
+        <v>44807.000000012849</v>
       </c>
       <c r="E51">
-        <v>0.89613350870091135</v>
+        <v>0.93307518166021186</v>
       </c>
       <c r="F51">
-        <v>1.2653740673105121</v>
+        <v>1.1307429873706381</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="C52">
-        <v>379770.9722566437</v>
+        <v>302885.98128337623</v>
       </c>
       <c r="D52">
-        <v>51555.000000003318</v>
+        <v>138844.00000002471</v>
       </c>
       <c r="E52">
-        <v>0.95410972411268991</v>
+        <v>0.76094931195686699</v>
       </c>
       <c r="F52">
-        <v>1.2220129114287359</v>
+        <v>1.297355576081316</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
         <v>57</v>
       </c>
-      <c r="B53" t="s">
-        <v>62</v>
-      </c>
       <c r="C53">
-        <v>314664.64148934861</v>
+        <v>383285.82254705508</v>
       </c>
       <c r="D53">
-        <v>167410.0000000119</v>
+        <v>27787.00000000565</v>
       </c>
       <c r="E53">
-        <v>0.79054118458672895</v>
+        <v>0.96294018532712833</v>
       </c>
       <c r="F53">
-        <v>1.21957419475366</v>
+        <v>1.0822573009605041</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="C54">
-        <v>395876.7338892243</v>
+        <v>357555.66717477358</v>
       </c>
       <c r="D54">
-        <v>41813.000000002947</v>
+        <v>276938.00000003021</v>
       </c>
       <c r="E54">
-        <v>0.99457270024953282</v>
+        <v>0.89829756322847543</v>
       </c>
       <c r="F54">
-        <v>1.1841501614195751</v>
+        <v>2.1284300920489199</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C55">
-        <v>349959.25602722663</v>
+        <v>389183.20704885281</v>
       </c>
       <c r="D55">
-        <v>82219.993974276586</v>
+        <v>17903.00000000689</v>
       </c>
       <c r="E55">
-        <v>0.87921287726323361</v>
+        <v>0.97775635694383145</v>
       </c>
       <c r="F55">
-        <v>1.179137830043024</v>
+        <v>1.1072660955526481</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C56">
-        <v>390712.81788847351</v>
+        <v>356694.29340278561</v>
       </c>
       <c r="D56">
-        <v>40366.000000006599</v>
+        <v>43874.00000000115</v>
       </c>
       <c r="E56">
-        <v>0.98159924300623425</v>
+        <v>0.89613350870091135</v>
       </c>
       <c r="F56">
-        <v>1.151337486300501</v>
+        <v>1.2653740673105121</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C57">
-        <v>371398.44608248671</v>
+        <v>332842.75692133512</v>
       </c>
       <c r="D57">
-        <v>44807.000000012849</v>
+        <v>166879.000000003</v>
       </c>
       <c r="E57">
-        <v>0.93307518166021186</v>
+        <v>0.83621059580223522</v>
       </c>
       <c r="F57">
-        <v>1.1307429873706381</v>
+        <v>1.6293767783199</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="C58">
-        <v>389688.98990794591</v>
+        <v>314664.64148934861</v>
       </c>
       <c r="D58">
-        <v>18272.999999999829</v>
+        <v>167410.0000000119</v>
       </c>
       <c r="E58">
-        <v>0.97902705001782464</v>
+        <v>0.79054118458672895</v>
       </c>
       <c r="F58">
-        <v>1.115205158173777</v>
+        <v>1.21957419475366</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C59">
-        <v>367996.0624382025</v>
+        <v>50764.519568364602</v>
       </c>
       <c r="D59">
-        <v>40159.15469945356</v>
+        <v>649009.00000027753</v>
       </c>
       <c r="E59">
-        <v>0.92452727369114329</v>
+        <v>0.12753718766939881</v>
       </c>
       <c r="F59">
-        <v>1.108548303911296</v>
+        <v>1.509741756225951</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C60">
-        <v>389183.20704885281</v>
+        <v>307667.11238647241</v>
       </c>
       <c r="D60">
-        <v>17903.00000000689</v>
+        <v>639752.00000451563</v>
       </c>
       <c r="E60">
-        <v>0.97775635694383145</v>
+        <v>0.77296108750310055</v>
       </c>
       <c r="F60">
-        <v>1.1072660955526481</v>
+        <v>1.0915893676706501</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C61">
-        <v>364819.53016200103</v>
+        <v>201458.85165758379</v>
       </c>
       <c r="D61">
-        <v>62891.000000023807</v>
+        <v>228613.00000000559</v>
       </c>
       <c r="E61">
-        <v>0.91654677872157631</v>
+        <v>0.50613096686384262</v>
       </c>
       <c r="F61">
-        <v>1.1044040427283199</v>
+        <v>1.0702100291740451</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C62">
-        <v>382946.31447513209</v>
+        <v>364819.53016200103</v>
       </c>
       <c r="D62">
-        <v>23042.0000000125</v>
+        <v>62891.000000023807</v>
       </c>
       <c r="E62">
-        <v>0.9620872292654481</v>
+        <v>0.91654677872157631</v>
       </c>
       <c r="F62">
-        <v>1.0997739167522951</v>
+        <v>1.1044040427283199</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C63">
-        <v>307667.11238647241</v>
+        <v>298315.80931657011</v>
       </c>
       <c r="D63">
-        <v>639752.00000451563</v>
+        <v>104820.0000000031</v>
       </c>
       <c r="E63">
-        <v>0.77296108750310055</v>
+        <v>0.74946753522051801</v>
       </c>
       <c r="F63">
-        <v>1.0915893676706501</v>
+        <v>2.0741650792052369</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C64">
-        <v>377734.50221215922</v>
+        <v>358536.27734945249</v>
       </c>
       <c r="D64">
-        <v>21333.000000031148</v>
+        <v>48479.000000053493</v>
       </c>
       <c r="E64">
-        <v>0.94899344084132431</v>
+        <v>0.90076117885887907</v>
       </c>
       <c r="F64">
-        <v>1.08956589969713</v>
+        <v>1.0538185817410139</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C65">
-        <v>397659.15418979042</v>
+        <v>195295.68846067501</v>
       </c>
       <c r="D65">
-        <v>15694.00000000024</v>
+        <v>261715.00000003359</v>
       </c>
       <c r="E65">
-        <v>0.99905072691681784</v>
+        <v>0.49064707165583732</v>
       </c>
       <c r="F65">
-        <v>1.08419059113002</v>
+        <v>1.296521423525953</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="C66">
-        <v>383285.82254705508</v>
+        <v>355462.35538638983</v>
       </c>
       <c r="D66">
-        <v>27787.00000000565</v>
+        <v>43096.000000001281</v>
       </c>
       <c r="E66">
-        <v>0.96294018532712833</v>
+        <v>0.89303847478095977</v>
       </c>
       <c r="F66">
-        <v>1.0822573009605041</v>
+        <v>0.94926745534823698</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="C67">
-        <v>382066.6850712974</v>
+        <v>370926.45426484832</v>
       </c>
       <c r="D67">
-        <v>37870.000000000036</v>
+        <v>858764</v>
       </c>
       <c r="E67">
-        <v>0.95987731057991199</v>
+        <v>0.93188938280824996</v>
       </c>
       <c r="F67">
-        <v>1.073089160258085</v>
+        <v>2.701600652449093</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C68">
-        <v>201458.85165758379</v>
+        <v>396542.59501553333</v>
       </c>
       <c r="D68">
-        <v>228613.00000000559</v>
+        <v>351095.00000001851</v>
       </c>
       <c r="E68">
-        <v>0.50613096686384262</v>
+        <v>0.99624556263747421</v>
       </c>
       <c r="F68">
-        <v>1.0702100291740451</v>
+        <v>1.5807215816432709</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>4</v>
+        <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="C69">
-        <v>379528.21906052699</v>
+        <v>381984.63032664981</v>
       </c>
       <c r="D69">
-        <v>20011.000000000651</v>
+        <v>143437.0000000103</v>
       </c>
       <c r="E69">
-        <v>0.95349984815614153</v>
+        <v>0.95967116204435488</v>
       </c>
       <c r="F69">
-        <v>1.065984153340336</v>
+        <v>1.382105547295928</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C70">
-        <v>358536.27734945249</v>
+        <v>397618.86043577321</v>
       </c>
       <c r="D70">
-        <v>48479.000000053493</v>
+        <v>202716.0000000016</v>
       </c>
       <c r="E70">
-        <v>0.90076117885887907</v>
+        <v>0.99894949573977354</v>
       </c>
       <c r="F70">
-        <v>1.0538185817410139</v>
+        <v>1.5425081148186379</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="C71">
-        <v>388101.79833486368</v>
+        <v>362015.74285358918</v>
       </c>
       <c r="D71">
-        <v>10385.862128765169</v>
+        <v>302873.0000000092</v>
       </c>
       <c r="E71">
-        <v>0.97503950219417468</v>
+        <v>0.90950274183954838</v>
       </c>
       <c r="F71">
-        <v>1.0321144123808801</v>
+        <v>1.821848478591946</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C72">
-        <v>381336.42890785559</v>
+        <v>390712.81788847351</v>
       </c>
       <c r="D72">
-        <v>16753.73575226765</v>
+        <v>40366.000000006599</v>
       </c>
       <c r="E72">
-        <v>0.95804266665625226</v>
+        <v>0.98159924300623425</v>
       </c>
       <c r="F72">
-        <v>1.0076493450575259</v>
+        <v>1.151337486300501</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C73">
-        <v>398037.00000000099</v>
+        <v>369491.98584294133</v>
       </c>
       <c r="D73">
-        <v>74451</v>
+        <v>171919.00000001461</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0.92828552582533885</v>
       </c>
       <c r="F73">
-        <v>1</v>
+        <v>1.8147017381297319</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C74">
-        <v>355462.35538638983</v>
+        <v>398037.00000000099</v>
       </c>
       <c r="D74">
-        <v>43096.000000001281</v>
+        <v>74451</v>
       </c>
       <c r="E74">
-        <v>0.89303847478095977</v>
+        <v>1</v>
       </c>
       <c r="F74">
-        <v>0.94926745534823698</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F74" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F74">
-      <sortCondition descending="1" ref="F1:F74"/>
+      <sortCondition ref="A1:A74"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
